--- a/artfynd/A 23043-2024 artfynd.xlsx
+++ b/artfynd/A 23043-2024 artfynd.xlsx
@@ -2830,11 +2830,11 @@
         <v>118142175</v>
       </c>
       <c r="B23" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/artfynd/A 23043-2024 artfynd.xlsx
+++ b/artfynd/A 23043-2024 artfynd.xlsx
@@ -2830,11 +2830,11 @@
         <v>118142175</v>
       </c>
       <c r="B23" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
